--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484018_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484018_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6181</v>
+        <v>9.327400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6836</v>
+        <v>7.5613</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9344</v>
+        <v>1.7661</v>
       </c>
       <c r="G2" t="n">
         <v>5.6793</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1129</v>
+        <v>1.8223</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2844</v>
+        <v>1.162</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8286</v>
+        <v>0.6602</v>
       </c>
       <c r="V2" t="n">
         <v>3.0162</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5078</v>
+        <v>6.1404</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5233</v>
+        <v>3.9314</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9846</v>
+        <v>2.209</v>
       </c>
       <c r="G3" t="n">
         <v>7.6482</v>
@@ -688,13 +688,13 @@
         <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1565</v>
+        <v>0.4761</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3798</v>
+        <v>0.7879</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5363</v>
+        <v>-0.3119</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2782</v>
+        <v>2.9212</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0624</v>
+        <v>2.2664</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2159</v>
+        <v>0.6548</v>
       </c>
       <c r="G4" t="n">
         <v>4.9775</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5667</v>
+        <v>0.2097</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1928</v>
+        <v>0.3968</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3739</v>
+        <v>-0.1872</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4724</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1523</v>
+        <v>2.8563</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2987</v>
+        <v>2.1149</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8536</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.5531</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5397</v>
+        <v>0.1643</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.1928</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0838</v>
+        <v>-0.0284</v>
       </c>
       <c r="V5" t="n">
         <v>0.9405</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8279</v>
+        <v>1.4019</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7996</v>
+        <v>2.2895</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9717</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>2.7799</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6513</v>
+        <v>0.2253</v>
       </c>
       <c r="T6" t="n">
-        <v>1.247</v>
+        <v>0.7369</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5958</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2065</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9484</v>
+        <v>1.1524</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8366</v>
+        <v>1.0407</v>
       </c>
       <c r="F7" t="n">
         <v>0.1118</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1133</v>
+        <v>0.3174</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1247</v>
+        <v>0.0794</v>
       </c>
       <c r="U7" t="n">
         <v>0.238</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6397</v>
+        <v>0.9152</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2272</v>
+        <v>0.8394</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4125</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0.552</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4399</v>
+        <v>-0.1644</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6858</v>
+        <v>-0.0736</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2459</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.266</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1913</v>
+        <v>-0.3686</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0082</v>
+        <v>-0.4575</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1995</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4763</v>
+        <v>-1.2921</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4489</v>
+        <v>-0.2725</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9251</v>
+        <v>-1.0196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.77</v>
+        <v>-1.426</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4085</v>
+        <v>-0.2313</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3615</v>
+        <v>-1.1946</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2937</v>
+        <v>0.1339</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.0412</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5637</v>
+        <v>0.175</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1936</v>
+        <v>-0.2154</v>
       </c>
       <c r="T9" t="n">
-        <v>2.222</v>
+        <v>0.754</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0284</v>
+        <v>-0.9694</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4724</v>
+        <v>0.9405</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1338</v>
+        <v>-0.8305</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6615</v>
+        <v>-0.543</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4723</v>
+        <v>-0.2875</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2921</v>
+        <v>0.4641</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2725</v>
+        <v>1.5575</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0196</v>
+        <v>-1.0934</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.426</v>
+        <v>0.3481</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2313</v>
+        <v>1.4675</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1946</v>
+        <v>-1.1194</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1339</v>
+        <v>0.116</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0412</v>
+        <v>0.09</v>
       </c>
       <c r="O10" t="n">
-        <v>0.175</v>
+        <v>0.026</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9806</v>
+        <v>-0.8347</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.2948</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5305</v>
+        <v>-1.1295</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9405</v>
+        <v>0.532</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>-0.266</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2411</v>
+        <v>-1.4156</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.645</v>
+        <v>-0.2162</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5961</v>
+        <v>-1.1995</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4641</v>
+        <v>0.4763</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5575</v>
+        <v>-0.4489</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0934</v>
+        <v>0.9251</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3481</v>
+        <v>0.77</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4675</v>
+        <v>0.4085</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1194</v>
+        <v>0.3615</v>
       </c>
       <c r="M11" t="n">
-        <v>0.116</v>
+        <v>-0.2937</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.026</v>
+        <v>0.5637</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9919</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2453</v>
+        <v>0.9692</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1928</v>
+        <v>0.9977</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4381</v>
+        <v>-0.0284</v>
       </c>
       <c r="V11" t="n">
-        <v>0.532</v>
+        <v>-1.4724</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0127</v>
+        <v>-1.7066</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1686</v>
+        <v>-2.8625</v>
       </c>
       <c r="F12" t="n">
         <v>1.1559</v>
@@ -1390,10 +1390,10 @@
         <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3514</v>
+        <v>0.6575</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.051</v>
+        <v>0.2551</v>
       </c>
       <c r="U12" t="n">
         <v>0.4024</v>
@@ -1426,7 +1426,7 @@
         <v>20.3935</v>
       </c>
       <c r="E13" t="n">
-        <v>15.9645</v>
+        <v>15.9644</v>
       </c>
       <c r="F13" t="n">
         <v>4.4291</v>
@@ -1438,10 +1438,10 @@
         <v>14.5631</v>
       </c>
       <c r="I13" t="n">
-        <v>9.392799999999998</v>
+        <v>9.392800000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>20.4842</v>
+        <v>20.48419999999999</v>
       </c>
       <c r="K13" t="n">
         <v>13.3598</v>
@@ -1459,7 +1459,7 @@
         <v>2.2681</v>
       </c>
       <c r="P13" t="n">
-        <v>-7.9353</v>
+        <v>-7.935300000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.8624</v>
@@ -1468,16 +1468,16 @@
         <v>8.927300000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>3.627199999999999</v>
+        <v>3.6273</v>
       </c>
       <c r="T13" t="n">
-        <v>5.5837</v>
+        <v>5.5838</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9565</v>
+        <v>-1.9566</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7459000000000007</v>
+        <v>0.7459000000000002</v>
       </c>
       <c r="W13" t="n">
         <v>6.759</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4179</v>
+        <v>1.7342</v>
       </c>
       <c r="E14" t="n">
-        <v>1.628</v>
+        <v>1.8321</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2101</v>
+        <v>-0.0979</v>
       </c>
       <c r="G14" t="n">
         <v>0.2329</v>
@@ -1546,13 +1546,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9341</v>
+        <v>-0.6178</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7368</v>
+        <v>-0.5327</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.532</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5603</v>
+        <v>0.1241</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7335</v>
+        <v>1.3253</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1732</v>
+        <v>-1.2012</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1244</v>
@@ -1624,13 +1624,13 @@
         <v>2.579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4348</v>
+        <v>-0.0014</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1508</v>
+        <v>0.7427</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.716</v>
+        <v>-0.744</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3373</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.017</v>
+        <v>0.0111</v>
       </c>
       <c r="E16" t="n">
         <v>-0.1045</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1156</v>
       </c>
       <c r="G16" t="n">
         <v>0.0267</v>
@@ -1702,13 +1702,13 @@
         <v>0.1984</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.242</v>
+        <v>-0.214</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2553</v>
+        <v>-0.0793</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.7358</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7871</v>
+        <v>-0.8151</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4463</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.6249</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6858</v>
+        <v>-0.4817</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1151</v>
+        <v>-0.1432</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SERRA CASTILLO</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2843</v>
+        <v>-0.9183</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9987</v>
+        <v>-2.522</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2831</v>
+        <v>1.6037</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.8987</v>
+        <v>-1.0459</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.086</v>
+        <v>-0.9073</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8127</v>
+        <v>-0.1386</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9856</v>
+        <v>-1.1391</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5252</v>
+        <v>-0.5794</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5108</v>
+        <v>-0.5597</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.9131</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.6112</v>
+        <v>-0.3279</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3019</v>
+        <v>0.4211</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8679</v>
+        <v>-0.666</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7573</v>
+        <v>-0.391</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8894</v>
+        <v>-0.275</v>
       </c>
       <c r="V18" t="n">
-        <v>2.9449</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2109</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>J. SERRA CASTILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5186</v>
+        <v>-2.0487</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9302</v>
+        <v>1.1825</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4116</v>
+        <v>-3.2312</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0459</v>
+        <v>-4.8987</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9073</v>
+        <v>-2.086</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1386</v>
+        <v>-2.8127</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1391</v>
+        <v>-0.9856</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5794</v>
+        <v>0.5252</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5597</v>
+        <v>-1.5108</v>
       </c>
       <c r="M19" t="n">
-        <v>0.09320000000000001</v>
+        <v>-3.9131</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3279</v>
+        <v>-2.6112</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4211</v>
+        <v>-1.3019</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
         <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2662</v>
+        <v>0.1035</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7991</v>
+        <v>0.9411</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4671</v>
+        <v>-0.8376</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.9449</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.2109</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9983</v>
+        <v>-4.2987</v>
       </c>
       <c r="E20" t="n">
-        <v>1.076</v>
+        <v>-3.397</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.0744</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8349</v>
+        <v>-4.1325</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.7494</v>
+        <v>-0.9623</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0854</v>
+        <v>-3.1702</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7791</v>
+        <v>-1.6848</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9398</v>
+        <v>-0.3672</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1606</v>
+        <v>-1.3177</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0557</v>
+        <v>-2.4476</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8097</v>
+        <v>-0.5951</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2461</v>
+        <v>-1.8525</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7855</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0679</v>
+        <v>0.163</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1168</v>
+        <v>0.0057</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1847</v>
+        <v>0.1572</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.881</v>
+        <v>0.266</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.6194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5665</v>
+        <v>-4.4745</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8051</v>
+        <v>0.4639</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7614</v>
+        <v>-4.9383</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1325</v>
+        <v>-3.8349</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9623</v>
+        <v>-3.7494</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1702</v>
+        <v>-0.0854</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6848</v>
+        <v>-1.7791</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3672</v>
+        <v>-1.9398</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3177</v>
+        <v>0.1606</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4476</v>
+        <v>-2.0557</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5951</v>
+        <v>-1.8097</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8525</v>
+        <v>-0.2461</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1049</v>
+        <v>-0.5441</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4024</v>
+        <v>0.5046</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2975</v>
+        <v>-1.0487</v>
       </c>
       <c r="V21" t="n">
-        <v>0.266</v>
+        <v>-1.881</v>
       </c>
       <c r="W21" t="n">
-        <v>0.266</v>
+        <v>1.7384</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1597</v>
+        <v>-4.6156</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9858</v>
+        <v>-1.5777</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1739</v>
+        <v>-3.0378</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0804</v>
@@ -2170,13 +2170,13 @@
         <v>2.9758</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8728</v>
+        <v>-0.3287</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0965</v>
+        <v>0.5047</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9694</v>
+        <v>-0.8333</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5719</v>
+        <v>-5.1476</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5715</v>
+        <v>-2.3675</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0004</v>
+        <v>-2.7802</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6524</v>
@@ -2248,13 +2248,13 @@
         <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.641</v>
+        <v>-0.2168</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5839</v>
+        <v>0.788</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.225</v>
+        <v>-1.0048</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0639</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.3934</v>
+        <v>-19.7133</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4291</v>
+        <v>-4.429099999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.9645</v>
+        <v>-15.2841</v>
       </c>
       <c r="G24" t="n">
         <v>-23.9559</v>
@@ -2326,13 +2326,13 @@
         <v>16.8629</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.6271</v>
+        <v>-2.9472</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9565</v>
+        <v>1.9567</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.5838</v>
+        <v>-4.9037</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7457999999999998</v>
